--- a/s12列表.xlsx
+++ b/s12列表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20367"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20368"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1370E-BABD-4778-9224-C67AD7225B13}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909567B8-E623-4394-BCBA-563EBDEE9545}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" activeTab="3" xr2:uid="{2781410C-061B-417E-B30A-B6223D4530F7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{2781410C-061B-417E-B30A-B6223D4530F7}"/>
   </bookViews>
   <sheets>
     <sheet name="星动" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,12 @@
     <sheet name="弦月" sheetId="3" r:id="rId3"/>
     <sheet name="泡泡" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">弹珠!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">泡泡!$A$1:$Q$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">弦月!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">星动!$A$1:$Q$23</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="41">
   <si>
     <t>首字母</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -125,6 +131,70 @@
   </si>
   <si>
     <t>那时有风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去爱你</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咏叹调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灯火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lost Princess</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饮中八仙歌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Left &amp; Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK (Prod. By GRAY)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨下整夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>踮起脚尖爱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ferrari</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transcendence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Altern-ate--H-el-ical//</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plunderer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔雀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -499,10 +569,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F6A7DC-6A61-4E21-B514-E1BA2689FA04}">
-  <dimension ref="A1:Q9"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -558,7 +629,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2">
         <v>6</v>
       </c>
@@ -567,83 +641,242 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>0</v>
+      </c>
       <c r="B3">
         <v>6</v>
       </c>
       <c r="C3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B9">
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q23" xr:uid="{59E69282-38D5-4250-BD1E-0CCC95681B3B}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -651,7 +884,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1551F913-FB20-48F8-A4AF-78D698FFD38B}">
-  <dimension ref="A1:Q9"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.375" customWidth="1"/>
@@ -710,95 +944,243 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3">
         <v>6</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B9">
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q22" xr:uid="{49F6C27F-AA68-4CAA-8E20-E31A7CECC333}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -806,7 +1188,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4550528-60A8-49C5-9265-24EEEE2E50D7}">
-  <dimension ref="A1:Q9"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.125" customWidth="1"/>
@@ -865,103 +1248,209 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1</v>
+      </c>
       <c r="B4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B9">
+    </row>
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C18" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q18" xr:uid="{955C23DD-653C-4F12-99E2-DBF80F99C301}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CDE56A-7D3F-4368-A062-12FACB044D9E}">
-  <dimension ref="A1:Q9"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -1020,89 +1509,276 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
         <v>24</v>
       </c>
-      <c r="D9">
-        <v>1</v>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q25" xr:uid="{52316E8B-890A-4914-9583-7EA0E182B63A}">
+    <filterColumn colId="0">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/s12列表.xlsx
+++ b/s12列表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20368"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Photon\Documents\GitHub\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909567B8-E623-4394-BCBA-563EBDEE9545}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" xr2:uid="{2781410C-061B-417E-B30A-B6223D4530F7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="星动" sheetId="1" r:id="rId1"/>
@@ -19,12 +18,12 @@
     <sheet name="泡泡" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">弹珠!$A$1:$Q$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">泡泡!$A$1:$Q$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">弦月!$A$1:$Q$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">星动!$A$1:$Q$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">弹珠!$A$1:$Q$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">泡泡!$A$1:$Q$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">弦月!$A$1:$Q$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">星动!$A$1:$Q$29</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="52">
   <si>
     <t>首字母</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -195,13 +194,57 @@
   </si>
   <si>
     <t>孔雀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果爱了解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slow Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尘埃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ドラマツルギー（拟剧论）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INVOKE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>なだめスかしNegotiation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尘埃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slow Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果爱了解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slow Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尘埃</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -257,7 +300,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -568,9 +611,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F6A7DC-6A61-4E21-B514-E1BA2689FA04}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="21.25" customWidth="1"/>
@@ -629,7 +671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -642,7 +684,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -651,202 +693,202 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
       <c r="C4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>0</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>0</v>
       </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C17" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -854,38 +896,99 @@
         <v>0</v>
       </c>
       <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
         <v>10</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28">
         <v>10</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q23" xr:uid="{59E69282-38D5-4250-BD1E-0CCC95681B3B}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1551F913-FB20-48F8-A4AF-78D698FFD38B}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17.375" customWidth="1"/>
@@ -944,7 +1047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -955,7 +1058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -966,7 +1069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -977,7 +1080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -989,207 +1092,241 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>0</v>
-      </c>
       <c r="B6">
         <v>6</v>
       </c>
       <c r="C6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>1</v>
-      </c>
-      <c r="B17">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C26" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27">
         <v>10</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C27" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q22" xr:uid="{49F6C27F-AA68-4CAA-8E20-E31A7CECC333}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4550528-60A8-49C5-9265-24EEEE2E50D7}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.125" customWidth="1"/>
@@ -1248,7 +1385,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1259,7 +1396,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1270,7 +1407,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1289,76 +1426,76 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1366,81 +1503,120 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>0</v>
       </c>
-      <c r="B17">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18">
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
         <v>10</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C22" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q18" xr:uid="{955C23DD-653C-4F12-99E2-DBF80F99C301}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1448,9 +1624,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09CDE56A-7D3F-4368-A062-12FACB044D9E}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -1509,7 +1684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1520,7 +1695,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1533,7 +1708,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -1542,7 +1717,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1555,7 +1730,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -1564,106 +1739,97 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>7</v>
       </c>
       <c r="C7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>1</v>
-      </c>
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>1</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>1</v>
-      </c>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1671,21 +1837,21 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1693,21 +1859,21 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1715,70 +1881,122 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30">
         <v>10</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q25" xr:uid="{52316E8B-890A-4914-9583-7EA0E182B63A}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
